--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>119776424</v>
       </c>
       <c r="B3" t="n">
-        <v>56655</v>
+        <v>56665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129086567</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>57646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129086567</v>
       </c>
       <c r="B4" t="n">
-        <v>57646</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129086567</v>
       </c>
       <c r="B4" t="n">
-        <v>57805</v>
+        <v>57807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -894,7 +894,7 @@
         <v>129086567</v>
       </c>
       <c r="B4" t="n">
-        <v>57807</v>
+        <v>57808</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17277-2023 artfynd.xlsx
+++ b/artfynd/A 17277-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119631629</v>
+        <v>129086567</v>
       </c>
       <c r="B2" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100137</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -753,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +783,7 @@
         <v>119776424</v>
       </c>
       <c r="B3" t="n">
-        <v>56665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,32 +881,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129086567</v>
+        <v>119631629</v>
       </c>
       <c r="B4" t="n">
-        <v>57825</v>
+        <v>57811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100137</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -964,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
